--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,96 @@
           <t>Oyster Composite Studio</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mushroom Felt Studio</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Alabaster Grid Studio</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cashmere Curve Studio</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ivory Rib Studio</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Parchment Arc Studio</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Satin Stone Studio</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Fog Linen Studio</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bone Clay Studio</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Dune Resin Studio</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Quartz Veil Studio</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Pebble Mist Studio</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Travertine Veil Studio</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Silica Horizon Studio</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Marble Dust Studio</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Porcelain Drift Studio</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Limestone Silk Studio</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Velvet Ash Studio</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Graphite Pearl Studio</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -637,6 +727,41 @@
       <c r="AC6" t="inlineStr">
         <is>
           <t>Chalk Mineral Studio</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Mineral Silk Studio</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Rice Paper Studio</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Ash Velvet Panel Studio</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Birch Mist Studio</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Arctic Felt Studio</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Cloudstone Studio</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Opal Mist Studio</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,31 @@
           <t>Terracota Style With Plant and Gym equipment in background</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Glacier Veil Studio</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Arctic Linen Studio</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Moonstone Plane Studio</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Porcelain Arc Studio</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Opal Grid Studio</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,6 +565,11 @@
           <t>Graphite Pearl Studio</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Opaline Panel Studio</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,6 +792,111 @@
       <c r="AJ6" t="inlineStr">
         <is>
           <t>Opal Mist Studio</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Talc Panel Studio</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Halo Composite Studio</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Moonwash Composite Studio</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Siltstone Horizon Studio</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Ivory Basalt Studio</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Dune Paper Studio</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Calcium Arc Studio</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Gypsum Fold Studio</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Velum Stone Studio</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Ecru Monolith Studio</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Ivory Relief Studio</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Putty Wave Studio</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sage Mist Panel Studio</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vanilla Seam Studio</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Sesame Horizon Studio</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Driftstone Layer Studio</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Cashstone Inlay Studio</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Dolomite Frame Studio</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Marshmallow Edge Studio</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Graphite Ribbon Studio</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>Nimbus Groove Studio</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE6"/>
+  <dimension ref="A1:BQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -416,6 +416,11 @@
           <t>Terracota Style With Plant and Gym equipment in background</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ivory Fold Studio</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -453,6 +458,66 @@
           <t>Opal Grid Studio</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Chalkstone Horizon Studio</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ivory Flute Studio</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cashmere Ridge Studio</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Dolomite Halo Studio</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Almond Seam Studio</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pebble Fold Studio</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Satin Dune Studio</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Mist Quartz Studio</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Calcium Curve Studio</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Silica Drift Studio</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Talc Cascade Studio</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Pumice Crest Studio</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -897,6 +962,66 @@
       <c r="BE6" t="inlineStr">
         <is>
           <t>Nimbus Groove Studio</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Avena Contour Studio</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Cottonstone Studio</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Pumice Plane Studio</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Kaolin Drift Studio</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Shellstone Sweep Studio</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>Fawn Radius Studio</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>Lunar Cast Studio</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>Mica Bloom Studio</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>Tufa Crest Studio</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>Calcite Veil Studio</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>Flaxstone Halo Studio</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>Biscuit Mesh Studio</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ6"/>
+  <dimension ref="A1:CF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,91 @@
           <t>Pumice Crest Studio</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Ecru Monolith Studio</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kaolin Panel Studio</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Marrow Ledger Studio</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Limestone Ribbon Studio</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Celestine Softplane Studio</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Nimbus Slab Studio</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Gypsum Veil Studio</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Bone Strata Studio</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Velour Clay Studio</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mica Frame Studio</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Ash Silk Studio</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Pearl Facet Studio</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Frostline Studio</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Aster Panel Studio</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Halo Seam Studio</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Selenite Channel Studio</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Calcite Edge Studio</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -635,6 +720,16 @@
           <t>Opaline Panel Studio</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Calcite Edge Studio</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Selenite Channel Studio</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1022,6 +1117,81 @@
       <c r="BQ6" t="inlineStr">
         <is>
           <t>Biscuit Mesh Studio</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Selenite Ledger Studio</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>Ashen Bevel Studio</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>Arctic Seam Studio</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>Auric Softplane Studio</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>Mallow Taper Studio</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>Ivory Chamfer Studio</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>Lustre Joint Studio</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>Vellum Cove Studio</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>Wheatline Studio</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>Oatline Reveal Studio</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>Parchstone Offset Studio</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>Bonecrest Studio</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>Chamois Facet Studio</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>Silica Band Studio</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>Nimbus Slate Studio</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -421,6 +421,356 @@
           <t>Ivory Fold Studio</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Talc Crest Studio</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Limestone Grid Studio</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Quartz Vein Studio</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sandstone Flute Studio</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Kaolin Ribbon Studio</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Dolomite Seam Studio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Chalk Arc Studio</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Almond Horizon Studio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Pumice Layer Studio</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Travertine Halo Studio</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ecru Monolith Plane</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Porcelain Frame Studio</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Oatline Panel Studio</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Mistline Relief Studio</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Bone Inset Studio</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Vanilla Reveal Studio</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Cashstone Groove Studio</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Greige Suede Sweep Studio</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Flax Clay Cove Studio</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Rice Paper Wash Studio</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Mica Veil Studio</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Soft Sage Mineral Sweep Studio</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Milkstone Radius Studio</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Frosted Resin Cove Studio</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Pale Birch Sweep Studio</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Powder Blue Casein Studio</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Warm Canvas Cove Studio</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Warm Putty Cove Studio</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Pale Olive Tadelakt Studio</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Oyster Felt Cove Studio</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Pale Raffia Weave Studio</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Cloud Linen Plaster Studio</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Honey Shell Microcement Set</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Sea Salt Stucco Sweep</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Pale Pewter Clay Sweep</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Chalky Lilac Cement Studio</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Dove Mineral Cove Studio</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gesso Plane Studio</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Pearl Barite Sweep</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Pale Soapstone Plane</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Pale Fawn Clay Curve</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Blush Calcite Cove</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Pale Zinc Limewash Plane</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Honed Granite Dust Cove</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Sanded Corian Plane Studio</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Selenite Wash Cove</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Warm Ash Veneer Cove</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Pale Terrazzo Mist Studio</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Pale Silica Matboard Sweep</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Warm Parch Sand Cove</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Cream Polymer Radius Studio</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Pale Cinder Rubber Cove</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Warm Feldspar Cove</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Buttermilk Microplaster Cove</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Pale Driftglass Resin Cove</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Warm Hemp Board Cove</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Pale Celadon Plaster Cove</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Eggshell Mineral Board Cove</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Soft Wheatstone Cove</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Pale Juniper Clay Cove</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Pale Aerofoam Radius Set</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Pale Oat Milk Render Cove</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Pale Nordic Clayboard Set</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>Warm Marzipan Ceramic Cove</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Pale Nougat Slab Cove</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>Pale Shellac Enamel Sweep</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>Pale Diatomite Cove</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>Pale Barley Fiber Cove</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Pale Tuffstone Cove</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>Pale Hornstone Sweep</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,6 +953,211 @@
           <t>Calcite Edge Studio</t>
         </is>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pale Reed Plaster Sweep</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Cloud Milk Microcement Cove</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Washed Birch Veneer Sweep</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Rice Paper Resin Cove</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pale Hempcrete Radius Set</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Warm Loess Render Cove</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Warm Soapstone Radius Set</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Oat Milk Claystone Cove</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Pale Jesmonite Radius Cove</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Frosted Milk Acrylic Cove</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Pale Tadelakt Radius Set</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Blush Mineral Resin Cove</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Pale Raku Plaster Cove</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pale Sanded Rubber Cove</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Warm Gesso Canvas Cove</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>Shell Lime Radius Cove</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Pale Maple Lamella Cove</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Ivory Wax Plaster Cove</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Champagne Alloy Curve Set</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>Soft Flax Fiber Cove</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>Pale Terrazzo Resin Cove</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>Soft Nubuck Curve Set</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Honed Honey Onyx Cove</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>Warm Enamel Radius Set</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Pale Linoleum Radius Set</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Pearl Corian Radius Set</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>Pale Suede Laminate Sweep</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>Pale Mohair Felt Sweep</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>Matte Milkglass Cove</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>Pale Ceramic Slip Cove</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>Ivory Paperclay Radius Set</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>Pale Algae Composite Sweep</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>Mist Mycelium Board Sweep</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>Pale Kapok Acoustic Sweep</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>Warm Basalt Powder Set</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>Pale Piqu‚ Fabric Sweep</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>Pale Satin Rubberite Sweep</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Pale Diatomite Sweep</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>Pale Bentonite Clay Sweep</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>Pale Zeolite Mineral Sweep</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>Ivory Aerogel Matte Sweep</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -728,6 +1283,21 @@
       <c r="Y4" t="inlineStr">
         <is>
           <t>Selenite Channel Studio</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Pale Birch Radius Studio</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Pale Pumice Wash Studio</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Warm Taupe Tadelakt Sweep</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF6"/>
+  <dimension ref="A1:CF7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1192,6 +1192,18 @@
       <c r="CF6" t="inlineStr">
         <is>
           <t>Nimbus Slate Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WHITE-BAGGY-JEANS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Warm Sandstone Plaster Cove</t>
         </is>
       </c>
     </row>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -1206,6 +1206,156 @@
           <t>Warm Sandstone Plaster Cove</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pale Celadon Silk-Cement Sweep</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quiet Lilac Acoustic Felt Cove</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Powder Blue Gypsum Radius</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pale Mushroom Limestone Sweep</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Muted Coral Paperclay Sweep</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pale Buttercream Mineral-Lacquer Cove</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Soft Pewter Wool-Cement Cove</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Faded Indigo Linoleum Cove</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Smoked Oak Fiberboard Radius</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Oat Hempcrete Radius</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Soft Graphite Cork-Rubber Cove</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Muted Olive Terrazzo-Resin Cove</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Frosted Opal Acrylic Radius</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Champagne Anodized-Aluminum Radius</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Desaturated Teal Casein-Board Cove</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sunwashed Ochre Limewash Cove</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Soft Cinnamon Paperstone Cove</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Muted Plum Microsuede Cove</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dusty Brick Sintered-Ceramic Cove</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pistachio Dolomite Cove</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pale Almond Marmorino Cove</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Dove Gray Porcelain-Slip Cove</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Midnight Navy Cotton-Velvet Cove</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Bleached Sycamore Veneer Radius</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Glacier Aqua Vitreous-Enamel Cove</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Muted Cobalt Jesmonite Cove</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Pale Apricot Scagliola Cove</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Warm Biscuit Kaolin-Render Cove</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Muted Garnet Oxide-Cement Cove</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Dusty Periwinkle Calcium-Silicate Cove</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d750000efd74353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R827ed1a23e554bc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -703,6 +703,36 @@
       <x:c r="AI4" t="str">
         <x:v>Cranberry Quartz-Flax Studio</x:v>
       </x:c>
+      <x:c r="AJ4" t="str">
+        <x:v>Pearl Sand Fine-Rake Plaster Studio</x:v>
+      </x:c>
+      <x:c r="AK4" t="str">
+        <x:v>Pale Apricot Mineral-Wash Studio</x:v>
+      </x:c>
+      <x:c r="AL4" t="str">
+        <x:v>Light Celadon Basket-Weave Render Studio</x:v>
+      </x:c>
+      <x:c r="AM4" t="str">
+        <x:v>Warm Ivory Split-Face Limestone Studio</x:v>
+      </x:c>
+      <x:c r="AN4" t="str">
+        <x:v>Mist Lavender Silk-Gesso Studio</x:v>
+      </x:c>
+      <x:c r="AO4" t="str">
+        <x:v>Powder Blue Micro-Fluted Clay Studio</x:v>
+      </x:c>
+      <x:c r="AP4" t="str">
+        <x:v>Soft Oat Travertine-Pore Studio</x:v>
+      </x:c>
+      <x:c r="AQ4" t="str">
+        <x:v>Blush Beige Cross-Trowel Studio</x:v>
+      </x:c>
+      <x:c r="AR4" t="str">
+        <x:v>Pale Buttercream Woven-Lime Studio</x:v>
+      </x:c>
+      <x:c r="AS4" t="str">
+        <x:v>Frost Mint Porcelain-Grain Studio</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R827ed1a23e554bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd0afac3551f64438"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1536,6 +1536,36 @@
       <x:c r="CC7" t="str">
         <x:v>Powder Aqua Suede-Plaster Studio</x:v>
       </x:c>
+      <x:c r="CD7" t="str">
+        <x:v>Light Sage Canvas-Plaster Studio</x:v>
+      </x:c>
+      <x:c r="CE7" t="str">
+        <x:v>Powder Lilac Crosshatch-Gesso Studio</x:v>
+      </x:c>
+      <x:c r="CF7" t="str">
+        <x:v>Warm Crema Ribbed-Stucco Studio</x:v>
+      </x:c>
+      <x:c r="CG7" t="str">
+        <x:v>Pale Stone Blue Sanded-Clay Studio</x:v>
+      </x:c>
+      <x:c r="CH7" t="str">
+        <x:v>Dusty Blush Fine-Flute Studio</x:v>
+      </x:c>
+      <x:c r="CI7" t="str">
+        <x:v>Pale Mint Pebble-Dash Lime Studio</x:v>
+      </x:c>
+      <x:c r="CJ7" t="str">
+        <x:v>Light Caramel Grasscloth-Plaster Studio</x:v>
+      </x:c>
+      <x:c r="CK7" t="str">
+        <x:v>Gentle Butter Yellow Scraped-Lime Studio</x:v>
+      </x:c>
+      <x:c r="CL7" t="str">
+        <x:v>Soft Mauve Pinstripe-Microcement Studio</x:v>
+      </x:c>
+      <x:c r="CM7" t="str">
+        <x:v>Muted Aqua Shell-Ripple Plaster Studio</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/image_prompter/USED-IMAGE-DESIGNS.xlsx
+++ b/image_prompter/USED-IMAGE-DESIGNS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd0afac3551f64438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2b4745ec66be433e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -733,6 +733,36 @@
       <x:c r="AS4" t="str">
         <x:v>Frost Mint Porcelain-Grain Studio</x:v>
       </x:c>
+      <x:c r="AT4" t="str">
+        <x:v>Pale Sky Linen-Plaster Studio</x:v>
+      </x:c>
+      <x:c r="AU4" t="str">
+        <x:v>Warm Sand Fine-Ripple Stucco Studio</x:v>
+      </x:c>
+      <x:c r="AV4" t="str">
+        <x:v>Soft Peach Cotton-Lime Studio</x:v>
+      </x:c>
+      <x:c r="AW4" t="str">
+        <x:v>Light Sage Horizontal-Rake Studio</x:v>
+      </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>Powder Lilac Micro-Dapple Studio</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>Creamy Almond Canvas-Render Studio</x:v>
+      </x:c>
+      <x:c r="AZ4" t="str">
+        <x:v>Pale Aqua Brushed-Clay Studio</x:v>
+      </x:c>
+      <x:c r="BA4" t="str">
+        <x:v>Blush Ivory Shell-Sand Studio</x:v>
+      </x:c>
+      <x:c r="BB4" t="str">
+        <x:v>Light Wheat Soft-Flute Studio</x:v>
+      </x:c>
+      <x:c r="BC4" t="str">
+        <x:v>Misty Periwinkle Fine-Felt Studio</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
